--- a/plantilla_reporte_ats.xlsx
+++ b/plantilla_reporte_ats.xlsx
@@ -10,22 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENTOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUCESOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRAFICA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="TENDENCIA">RESUMEN!$C$11</definedName>
-    <definedName name="EVENTOS_TOT">RESUMEN!$C$12</definedName>
-    <definedName name="CONFIANZA">RESUMEN!$C$13</definedName>
-    <definedName name="UE_ID">RESUMEN!$C$16</definedName>
-    <definedName name="UE_FECHA">RESUMEN!$C$17</definedName>
-    <definedName name="UE_CAUSA">RESUMEN!$C$18</definedName>
-    <definedName name="UE_PROB">RESUMEN!$C$19</definedName>
-    <definedName name="UE_T">RESUMEN!$C$20</definedName>
-    <definedName name="UE_V">RESUMEN!$C$21</definedName>
-    <definedName name="UE_LECTURA">RESUMEN!$C$22</definedName>
-    <definedName name="LINEA_BASE">RESUMEN!$C$24</definedName>
-    <definedName name="SCORE">RESUMEN!$B$7</definedName>
-    <definedName name="BANDA">RESUMEN!$E$7</definedName>
-    <definedName name="GENERADO">RESUMEN!$C$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'RESUMEN'!$A$1:$G$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,53 +32,91 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FFDCE6F1"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
     </font>
     <font>
       <b val="1"/>
     </font>
     <font>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="FF1F4E79"/>
       <sz val="48"/>
     </font>
     <font>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="FF595959"/>
       <sz val="18"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="00595959"/>
-      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,17 +125,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,73 +166,117 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
-        <color rgb="009C0006"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+        <sz val="18"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="00006100"/>
+        <b val="1"/>
+        <color rgb="FF375623"/>
+        <sz val="18"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="FFE2EFDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="009C6500"/>
+        <b val="1"/>
+        <color rgb="FF9C6500"/>
+        <sz val="18"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
+          <fgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+        <sz val="18"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -268,10 +353,446 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Evolución del score (0–100) por evento</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'EVENTOS'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="1F4E79"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'EVENTOS'!$A$2:$A$1001</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'EVENTOS'!$K$2:$K$1001</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <majorUnit val="20"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'EVENTOS'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="1F4E79"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'EVENTOS'!$A$2:$A$1001</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'EVENTOS'!$K$2:$K$1001</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <majorUnit val="20"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'EVENTOS'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="1F4E79"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'EVENTOS'!$A$2:$A$1001</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'EVENTOS'!$D$2:$D$1001</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'EVENTOS'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'EVENTOS'!$A$2:$A$1001</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'EVENTOS'!$E$2:$E$1001</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <logBase val="10"/>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6840000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaEventos" displayName="TablaEventos" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaEventos" displayName="TablaEventos" ref="A1:O2" headerRowCount="1">
+  <autoFilter ref="A1:O2"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="N°"/>
     <tableColumn id="2" name="Fecha y hora"/>
     <tableColumn id="3" name="Tipo / Causa"/>
@@ -283,15 +804,19 @@
     <tableColumn id="9" name="Potencia (W)"/>
     <tableColumn id="10" name="Pen."/>
     <tableColumn id="11" name="Score"/>
+    <tableColumn id="12" name="S (VA)"/>
+    <tableColumn id="13" name="Q (var)"/>
+    <tableColumn id="14" name="FP"/>
+    <tableColumn id="15" name="Sin suministro (s)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TablaSucesos" displayName="TablaSucesos" ref="A1:G2" headerRowCount="1">
-  <autoFilter ref="A1:G2"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TablaSucesos" displayName="TablaSucesos" ref="A1:H2" headerRowCount="1">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="Fecha y hora"/>
     <tableColumn id="2" name="Fuente"/>
     <tableColumn id="3" name="Cambio"/>
@@ -299,6 +824,7 @@
     <tableColumn id="5" name="Hz"/>
     <tableColumn id="6" name="Duró (s)"/>
     <tableColumn id="7" name="Diagnóstico probable"/>
+    <tableColumn id="8" name="FP"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -593,11 +1119,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F28"/>
+  <dimension ref="B2:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -605,38 +1131,45 @@
     <col width="2.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>REPORTE DEL ATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Módulo Retrofit No Invasivo — INTEC PG2</t>
+          <t>Reporte del ATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Módulo Retrofit No Invasivo — INTEC Capstone Project II</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Generado:</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Perfil de Rendimiento</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>de 100</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>OPTIMO</t>
         </is>
@@ -644,151 +1177,228 @@
     </row>
     <row r="8"/>
     <row r="9"/>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="10">
+        <f>IF(ISNUMBER(SEARCH("PTIM",E7)),"El ATS opera de forma óptima. No requiere ninguna acción.",IF(ISNUMBER(SEARCH("VIGIL",E7)),"El ATS funciona bien, con señales leves de desgaste. Conviene observarlo.",IF(ISNUMBER(SEARCH("ATENC",E7)),"El rendimiento está degradado. Se recomienda programar una revisión.",IF(ISNUMBER(SEARCH("CRIT",E7)),"Rendimiento crítico. El ATS requiere intervención inmediata.","Sin datos suficientes del perfil."))))</f>
+        <v/>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Tendencia:</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Eventos registrados:</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Confianza del cálculo:</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>ÚLTIMO EVENTO</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Evento #</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="C16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Fecha y hora</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="C17" s="13" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Causa estimada</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+      <c r="C18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Posibles causas</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="C19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Tiempo de conmutación</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Tiempo de conmutación (ms)</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>V red / V entrante</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>V red / V entrante (V)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Lectura</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
+      <c r="C22" s="13" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Línea base:</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Nota: la causa es una estimación automática por reglas (ISO 17359). Margen de error: tensión/corriente ±0.5%, frecuencia ±0.1 Hz (IEC 61557-12), tiempo ±5 ms. La evaluación normativa (NFPA 110) corresponde a mantenimiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="C24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Escala del perfil:</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Crítico &lt; 50</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Atención 50–69</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Vigilancia 70–89</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>Óptimo ≥ 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Nota: la causa es una estimación automática por reglas sobre los datos medidos. El score es una media móvil: se recupera de forma gradual con cada operación normal y baja cuando hay deterioro sostenido del ATS. La evidencia original permanece en la microSD del módulo.</t>
+        </is>
+      </c>
+    </row>
     <row r="28"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>ANÁLISIS PREDICTIVO DEL MECANISMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Transferencia RED→GEN</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Retransferencia GEN→RED</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Método: Kalman (nivel y tendencia) + CUSUM (deterioro sostenido) + vida útil con confianza 90% — ISO 17359. Calculado en la PC al exportar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Modelo: score por media móvil exponencial (EWMA) sobre la calidad de cada evento, con línea base robusta (mediana + IQR de 10 eventos). Normativa: ISO 17359 — monitoreo de condición de máquinas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
     <mergeCell ref="E7:F9"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="B26:F28"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="C20:F20"/>
     <mergeCell ref="B7:C9"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B27:F28"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C19:F19"/>
   </mergeCells>
+  <conditionalFormatting sqref="E7:F9">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="PTIM">
+      <formula>NOT(ISERROR(SEARCH("PTIM",E7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="VIGIL">
+      <formula>NOT(ISERROR(SEARCH("VIGIL",E7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" text="ATENC">
+      <formula>NOT(ISERROR(SEARCH("ATENC",E7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="3" text="CRIT">
+      <formula>NOT(ISERROR(SEARCH("CRIT",E7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -798,12 +1408,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -812,6 +1422,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,6 +1484,26 @@
           <t>Score</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>S (VA)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Q (var)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Sin suministro (s)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -888,7 +1522,6 @@
       <c r="D2" t="n">
         <v>3.4</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>127.5</v>
       </c>
@@ -907,19 +1540,20 @@
       <c r="K2" t="n">
         <v>100</v>
       </c>
+      <c r="L2" t="n">
+        <v>112</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:K1000">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>$J2&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>ISNUMBER(SEARCH("normal",$C2))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
-      <formula>OR(ISNUMBER(SEARCH("externa",$C2)),ISNUMBER(SEARCH("debil",$C2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
@@ -934,16 +1568,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="95" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,6 +1617,11 @@
           <t>Diagnóstico probable</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1005,26 +1645,73 @@
       <c r="E2" t="n">
         <v>60.02</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Fuente normalizada</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:G1000">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>OR(ISNUMBER(SEARCH("SIN_TENSION",$C2)),ISNUMBER(SEARCH("SIN_COM",$C2)),ISNUMBER(SEARCH("SOBRETENSION",$C2)))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>ISNUMBER(SEARCH("OK",$C2))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Evolución del score (0–100) — subidas y bajadas por evento</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Modelo: score por media móvil exponencial (EWMA) sobre la calidad de cada evento, con línea base robusta (mediana + IQR de 10 eventos). Normativa: ISO 17359 — monitoreo de condición de máquinas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Tiempo de conmutación por evento en ms — escala logarítmica (curva de degradación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="23" t="n"/>
+    </row>
+    <row r="40" ht="46" customHeight="1">
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Modelo: tendencia por filtro de Kalman (nivel y pendiente) + CUSUM para deterioro sostenido; vida útil por cruce del umbral 1.5× la base, con confianza 90%. Normativa: ISO 17359; tiempo de transferencia conforme a NFPA 110 (≤ 10 s).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B40:H40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>